--- a/benchmarks/business_workflow_lab/templates/project_template.xlsx
+++ b/benchmarks/business_workflow_lab/templates/project_template.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1311,46 +1311,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AmountTWD</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>原幣金額 × 匯率（fx_rates.csv），四捨五入 ROUND_HALF_UP 至兩位小數；不同幣別的原幣金額不可直接相加。</t>
+          <t>欄寬、凍結窗格、自動篩選、字型與填色保留模板設定，不要調整或自動調整欄寬。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>All detail sheets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>OrderID: text (文字，保留前導零)</t>
+          <t>來源沒有的值留空（空白儲存格），不要填 N/A、0 或自行推測的值。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>All sheets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>AmountTWD</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>ProjectID: text (文字，保留前導零)</t>
+          <t>原幣金額 × 匯率（fx_rates.csv），四捨五入 ROUND_HALF_UP 至兩位小數；不同幣別的原幣金額不可直接相加。</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>CustomerID: text (文字，保留前導零)</t>
+          <t>OrderID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>OrderDate: date YYYY-MM-DD</t>
+          <t>ProjectID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Status: text</t>
+          <t>CustomerID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Currency: text</t>
+          <t>OrderDate: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>NetAmount: number, 2 decimals (0.00)</t>
+          <t>Status: text</t>
         </is>
       </c>
     </row>
@@ -1447,46 +1447,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>AmountTWD: number, 2 decimals (0.00)</t>
+          <t>Currency: text</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>InvoiceID: text (文字，保留前導零)</t>
+          <t>NetAmount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>OrderID: text (文字，保留前導零)</t>
+          <t>AmountTWD: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>ProjectID: text (文字，保留前導零)</t>
+          <t>InvoiceID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>CustomerID: text (文字，保留前導零)</t>
+          <t>OrderID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>InvoiceDate: date YYYY-MM-DD</t>
+          <t>ProjectID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>DueDate: date YYYY-MM-DD</t>
+          <t>CustomerID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Currency: text</t>
+          <t>InvoiceDate: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Amount: number, 2 decimals (0.00)</t>
+          <t>DueDate: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>PaidAmount: number, 2 decimals (0.00)</t>
+          <t>Currency: text</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Balance: number, 2 decimals (0.00)</t>
+          <t>Amount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1634,46 +1634,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>BalanceTWD: number, 2 decimals (0.00)</t>
+          <t>PaidAmount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>ExpenseID: text (文字，保留前導零)</t>
+          <t>Balance: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>ProjectID: text (文字，保留前導零)</t>
+          <t>BalanceTWD: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>EmployeeID: text (文字，保留前導零)</t>
+          <t>ExpenseID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>ExpenseDate: date YYYY-MM-DD</t>
+          <t>ProjectID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Status: text</t>
+          <t>EmployeeID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Currency: text</t>
+          <t>ExpenseDate: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Amount: number, 2 decimals (0.00)</t>
+          <t>Status: text</t>
         </is>
       </c>
     </row>
@@ -1770,46 +1770,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>AmountTWD: number, 2 decimals (0.00)</t>
+          <t>Currency: text</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>QuoteID: text (文字，保留前導零)</t>
+          <t>Amount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>ProjectID: text (文字，保留前導零)</t>
+          <t>AmountTWD: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>CustomerID: text (文字，保留前導零)</t>
+          <t>QuoteID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>QuoteDate: date YYYY-MM-DD</t>
+          <t>ProjectID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>ValidUntil: date YYYY-MM-DD</t>
+          <t>CustomerID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Status: text</t>
+          <t>QuoteDate: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Currency: text</t>
+          <t>ValidUntil: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>NetAmount: number, 2 decimals (0.00)</t>
+          <t>Status: text</t>
         </is>
       </c>
     </row>
@@ -1923,78 +1923,112 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>AmountTWD: number, 2 decimals (0.00)</t>
+          <t>Currency: text</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>J / K</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Balance = Amount − PaidAmount；BalanceTWD 為 Balance 換算 TWD。</t>
+          <t>NetAmount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A4:E4 / row 5+</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>每個專案一列：OrderTWD 訂單金額、InvoiceBalanceTWD 發票未收金額、ApprovedExpenseTWD 核准支出、AcceptedQuoteTWD 已接受報價，皆為 TWD；各來源分開彙總，不互相加總。</t>
+          <t>AmountTWD: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B2:E2</t>
+          <t>J / K</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>公式 =SUM(B5:B{最後資料列}) 等，填入資料後延伸到最後一列；沒有資料時保留 B5:B5。</t>
+          <t>Balance = Amount − PaidAmount；BalanceTWD 為 Balance 換算 TWD。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A4:E4 / row 5+</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>每個專案一列：OrderTWD 訂單金額、InvoiceBalanceTWD 發票未收金額、ApprovedExpenseTWD 核准支出、AcceptedQuoteTWD 已接受報價，皆為 TWD；各來源分開彙總，不互相加總。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>B2:E2</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>公式 =SUM(B5:B{最後資料列}) 等，填入資料後延伸到最後一列；沒有資料時保留 B5:B5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Exceptions</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>A4:D4 / row 5+</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Source 為 Orders / Invoices / Expenses / Quotes，DocumentID 為來源文件 ID，Reason 為原因（例如 Overdue）。</t>
         </is>
